--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.72287009072259</v>
+        <v>7.429966389742421</v>
       </c>
       <c r="D2" t="n">
-        <v>20.39010243392065</v>
+        <v>3.313391645512106</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76505650309443</v>
+        <v>2.724321681752845</v>
       </c>
       <c r="F2" t="n">
-        <v>21.65296774572429</v>
+        <v>3.518607258680198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>84.20617095698563</v>
+        <v>13.68350278051017</v>
       </c>
       <c r="D3" t="n">
-        <v>70.33328698802002</v>
+        <v>11.42915913555325</v>
       </c>
       <c r="E3" t="n">
-        <v>16.76505650309443</v>
+        <v>2.724321681752845</v>
       </c>
       <c r="F3" t="n">
-        <v>21.65296774572429</v>
+        <v>3.518607258680198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.37736483171837</v>
+        <v>12.57382178515424</v>
       </c>
       <c r="D4" t="n">
-        <v>60.8241748592057</v>
+        <v>9.883928414620927</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76505650309443</v>
+        <v>2.724321681752845</v>
       </c>
       <c r="F4" t="n">
-        <v>21.65296774572429</v>
+        <v>3.518607258680198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
